--- a/data/seed/portfolio/L-2024-7564/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2024-7564/vypiska_2026-07_09.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I165"/>
+  <dimension ref="A1:I192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -558,33 +558,33 @@
           <t>100</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n">
-        <v>6011000</v>
-      </c>
-      <c r="D10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n">
+        <v>5667000</v>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zarafshon Moy XK</t>
+          <t>Saodat Mehmonxona AJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>299258731</t>
+          <t>326355628</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000631845380001</t>
+          <t>20208000431759957001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №91/26</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №1098</t>
         </is>
       </c>
     </row>
@@ -600,32 +600,32 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>8588000</v>
+        <v>8738000</v>
       </c>
       <c r="D11" s="2" t="n"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Farovon Sut MChJ</t>
+          <t>Xiva Moy MChJ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>287785562</t>
+          <t>286051560</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000674331595001</t>
+          <t>20208000706886355001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №213/26</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №8/26, QQS bilan</t>
         </is>
       </c>
     </row>
@@ -642,31 +642,31 @@
       </c>
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="n">
-        <v>4845000</v>
+        <v>4299000</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Guliston Mebel MChJ</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>242263351</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000437095317001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №137/26 от 03.07.2026</t>
+          <t>Shartnoma №137/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
@@ -683,31 +683,31 @@
       </c>
       <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="n">
-        <v>1116000</v>
+        <v>2237000</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Guliston Mebel MChJ</t>
+          <t>Denov Moy AJ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>242263351</t>
+          <t>249720994</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000437095317001</t>
+          <t>20208000548053460001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №19/26 от 03.07.2026</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №3848</t>
         </is>
       </c>
     </row>
@@ -722,40 +722,40 @@
           <t>104</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
-        <v>7066000</v>
-      </c>
-      <c r="D14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n">
+        <v>991000</v>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro MChJ</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>208630043</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000506769926001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №180/26 от 03.07.2026, НДС 12%</t>
+          <t>Shartnoma №19/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>03.07.2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -763,33 +763,33 @@
           <t>105</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="n">
-        <v>2521000</v>
-      </c>
+      <c r="C15" s="2" t="n">
+        <v>3874000</v>
+      </c>
+      <c r="D15" s="2" t="n"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Guliston Mebel MChJ</t>
+          <t>Shodlik Logistik MChJ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>242263351</t>
+          <t>308407012</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000437095317001</t>
+          <t>20208000844690983001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №6175 за поставленный товар</t>
+          <t>Оплата за транспортные услуги по договору №22/26</t>
         </is>
       </c>
     </row>
@@ -806,31 +806,31 @@
       </c>
       <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="n">
-        <v>1628000</v>
+        <v>1444000</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Guliston Mebel MChJ</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>242263351</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000437095317001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №7225 за поставленный товар</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №7225</t>
         </is>
       </c>
     </row>
@@ -847,31 +847,31 @@
       </c>
       <c r="C17" s="2" t="n"/>
       <c r="D17" s="2" t="n">
-        <v>1003000</v>
+        <v>1055000</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Guliston Mebel MChJ</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>242263351</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000437095317001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №249 за поставленный товар</t>
+          <t>Tovar uchun to'lov, hisob-faktura №8767 06.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
@@ -888,31 +888,31 @@
       </c>
       <c r="C18" s="2" t="n"/>
       <c r="D18" s="2" t="n">
-        <v>698000</v>
+        <v>890000</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mehnat Metall MChJ</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>385263556</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000864317599001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №3403 за поставленный товар</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №249</t>
         </is>
       </c>
     </row>
@@ -927,33 +927,33 @@
           <t>109</t>
         </is>
       </c>
-      <c r="C19" s="2" t="n">
-        <v>4972000</v>
-      </c>
-      <c r="D19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n">
+        <v>502000</v>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Zarafshon Moy XK</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>299258731</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000631845380001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №186/26</t>
+          <t>Mahsulot uchun to'lov, shartnoma №79/26, QQS 12%</t>
         </is>
       </c>
     </row>
@@ -968,33 +968,33 @@
           <t>110</t>
         </is>
       </c>
-      <c r="C20" s="2" t="n">
-        <v>5191000</v>
-      </c>
-      <c r="D20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n">
+        <v>493000</v>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Zarafshon Moy XK</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>299258731</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20208000631845380001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №57/26</t>
+          <t>Оплата за продукцию по дог. №116/26, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -1010,17 +1010,22 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>5567000</v>
+        <v>2824000</v>
       </c>
       <c r="D21" s="2" t="n"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Oqsaroy Bank ATB</t>
+          <t>Xiva Moy MChJ</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>286051560</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000706886355001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1030,7 +1035,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Заработная плата за июнь 2026 г. (перечисление на пластиковые карты)</t>
+          <t>Оплата за упаковочные материалы, с/ф №3332</t>
         </is>
       </c>
     </row>
@@ -1046,39 +1051,39 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>41320000</v>
+        <v>3729000</v>
       </c>
       <c r="D22" s="2" t="n"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro MChJ</t>
+          <t>Zafar Qurilish AJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>208630043</t>
+          <t>272008031</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000506769926001</t>
+          <t>20208000571561011001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №79/26</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №286/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08.07.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1087,39 +1092,34 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>902000</v>
+        <v>5567000</v>
       </c>
       <c r="D23" s="2" t="n"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Chirchiq Qurilish MChJ</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>210732548</t>
+          <t>Oqsaroy Bank ATB</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000891752591001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Аренда помещения за июль, дог. №82/23</t>
+          <t>Ish haqi to'lovi iyun 2026 (plastik kartalarga)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08.07.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1128,39 +1128,39 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>5217000</v>
+        <v>5718000</v>
       </c>
       <c r="D24" s="2" t="n"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro MChJ</t>
+          <t>Afrosiyob Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>208630043</t>
+          <t>363004325</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000506769926001</t>
+          <t>20208000676992684001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №4439</t>
+          <t>Tovarlar uchun to'lov h/f №9255</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09.07.2026</t>
+          <t>07.07.2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1170,38 +1170,38 @@
       </c>
       <c r="C25" s="2" t="n"/>
       <c r="D25" s="2" t="n">
-        <v>1148000</v>
+        <v>969000</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bunyodkor Qog'oz MChJ</t>
+          <t>Saodat Mehmonxona AJ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>321993740</t>
+          <t>326355628</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000028573651001</t>
+          <t>20208000431759957001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №7828 от 09.07.2026, в т.ч. НДС 12%</t>
+          <t>Shartnoma №82/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09.07.2026</t>
+          <t>07.07.2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1209,40 +1209,40 @@
           <t>116</t>
         </is>
       </c>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n">
-        <v>1092000</v>
-      </c>
+      <c r="C26" s="2" t="n">
+        <v>5150000</v>
+      </c>
+      <c r="D26" s="2" t="n"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Guliston Mebel MChJ</t>
+          <t>Xiva Moy MChJ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>242263351</t>
+          <t>286051560</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000437095317001</t>
+          <t>20208000706886355001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №9383</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №118/26</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>07.07.2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1250,40 +1250,40 @@
           <t>117</t>
         </is>
       </c>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n">
-        <v>4052000</v>
-      </c>
+      <c r="C27" s="2" t="n">
+        <v>7601000</v>
+      </c>
+      <c r="D27" s="2" t="n"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Guliston Mebel MChJ</t>
+          <t>Shodlik Logistik MChJ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>242263351</t>
+          <t>308407012</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000437095317001</t>
+          <t>20208000844690983001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №19/26 от 10.07.2026</t>
+          <t>Xom ashyo uchun to'lov, shartn. №43/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>08.07.2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1291,23 +1291,23 @@
           <t>118</t>
         </is>
       </c>
-      <c r="C28" s="2" t="n"/>
-      <c r="D28" s="2" t="n">
-        <v>1763000</v>
-      </c>
+      <c r="C28" s="2" t="n">
+        <v>902000</v>
+      </c>
+      <c r="D28" s="2" t="n"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Jizzax Meva-Sabzavot AJ</t>
+          <t>Yulduz Qurilish MChJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>392497209</t>
+          <t>273254868</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000475480534001</t>
+          <t>20208000175259122001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1317,14 +1317,14 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №3344 за поставленный товар</t>
+          <t>Арендная плата за июль 2026 г. по договору №96/21</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>09.07.2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1334,38 +1334,38 @@
       </c>
       <c r="C29" s="2" t="n"/>
       <c r="D29" s="2" t="n">
-        <v>635000</v>
+        <v>653000</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Mehnat Metall MChJ</t>
+          <t>Denov Moy AJ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>385263556</t>
+          <t>249720994</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000864317599001</t>
+          <t>20208000548053460001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №20/26, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartn. №288/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>10.07.2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1375,38 +1375,38 @@
       </c>
       <c r="C30" s="2" t="n"/>
       <c r="D30" s="2" t="n">
-        <v>555000</v>
+        <v>3596000</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Jizzax Meva-Sabzavot AJ</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>392497209</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000475480534001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №3751 13.07.2026, QQS bilan</t>
+          <t>Shartnoma №19/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>10.07.2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1414,23 +1414,23 @@
           <t>121</t>
         </is>
       </c>
-      <c r="C31" s="2" t="n">
-        <v>2629000</v>
-      </c>
-      <c r="D31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n">
+        <v>1565000</v>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro MChJ</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>208630043</t>
+          <t>299374010</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000506769926001</t>
+          <t>20208000857365140001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №10/26 от 13.07.2026, НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №3344</t>
         </is>
       </c>
     </row>
@@ -1455,40 +1455,40 @@
           <t>122</t>
         </is>
       </c>
-      <c r="C32" s="2" t="n">
-        <v>5952000</v>
-      </c>
-      <c r="D32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n">
+        <v>2391000</v>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro MChJ</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>208630043</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000506769926001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №127/26</t>
+          <t>Оплата по счет-фактуре №2928 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>14.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1496,40 +1496,40 @@
           <t>123</t>
         </is>
       </c>
-      <c r="C33" s="2" t="n">
-        <v>3571000</v>
-      </c>
-      <c r="D33" s="2" t="n"/>
+      <c r="C33" s="2" t="n"/>
+      <c r="D33" s="2" t="n">
+        <v>1213000</v>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro MChJ</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>208630043</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000506769926001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №3077</t>
+          <t>Tovar uchun to'lov, hisob-faktura №8516 13.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1539,31 +1539,31 @@
       </c>
       <c r="C34" s="2" t="n"/>
       <c r="D34" s="2" t="n">
-        <v>3413000</v>
+        <v>563000</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mehnat Metall MChJ</t>
+          <t>Saodat Mehmonxona AJ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>385263556</t>
+          <t>326355628</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20208000864317599001</t>
+          <t>20208000431759957001</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №9486 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>Mahsulot uchun to'lov, shartnoma №20/26, QQS 12%</t>
         </is>
       </c>
     </row>
@@ -1580,31 +1580,31 @@
       </c>
       <c r="C35" s="2" t="n"/>
       <c r="D35" s="2" t="n">
-        <v>1042000</v>
+        <v>3029000</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Guliston Mebel MChJ</t>
+          <t>Saodat Mehmonxona AJ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>242263351</t>
+          <t>326355628</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20208000437095317001</t>
+          <t>20208000431759957001</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №236/26 от 15.07.2026</t>
+          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №9486</t>
         </is>
       </c>
     </row>
@@ -1619,33 +1619,33 @@
           <t>126</t>
         </is>
       </c>
-      <c r="C36" s="2" t="n">
-        <v>759000</v>
-      </c>
-      <c r="D36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n">
+        <v>1306000</v>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Iyun oyi uchun ijtimoiy soliq</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4998</t>
         </is>
       </c>
     </row>
@@ -1660,40 +1660,40 @@
           <t>127</t>
         </is>
       </c>
-      <c r="C37" s="2" t="n">
-        <v>759000</v>
-      </c>
-      <c r="D37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n">
+        <v>700000</v>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Налог на доходы физических лиц за июнь 2026 г.</t>
+          <t>Shartnoma №191/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1701,40 +1701,40 @@
           <t>128</t>
         </is>
       </c>
-      <c r="C38" s="2" t="n"/>
-      <c r="D38" s="2" t="n">
-        <v>2990000</v>
-      </c>
+      <c r="C38" s="2" t="n">
+        <v>759000</v>
+      </c>
+      <c r="D38" s="2" t="n"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Mehnat Metall MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>385263556</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000864317599001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №1870 ОТ 16.07.2026, В Т.Ч. НДС 12%</t>
+          <t>Ijtimoiy soliq iyun 2026</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1742,40 +1742,40 @@
           <t>129</t>
         </is>
       </c>
-      <c r="C39" s="2" t="n"/>
-      <c r="D39" s="2" t="n">
-        <v>804000</v>
-      </c>
+      <c r="C39" s="2" t="n">
+        <v>759000</v>
+      </c>
+      <c r="D39" s="2" t="n"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Guliston Mebel MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>242263351</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000437095317001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №8004 за поставленный товар</t>
+          <t>JISMONIY SHAXSLAR DAROMAD SOLIG'I IYUN 2026</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1784,22 +1784,22 @@
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>6825000</v>
+        <v>21920000</v>
       </c>
       <c r="D40" s="2" t="n"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro MChJ</t>
+          <t>Xiva Moy MChJ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>208630043</t>
+          <t>286051560</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20208000506769926001</t>
+          <t>20208000706886355001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -1809,14 +1809,14 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №3548</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №136/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1826,38 +1826,38 @@
       </c>
       <c r="C41" s="2" t="n"/>
       <c r="D41" s="2" t="n">
-        <v>9566000</v>
+        <v>13197000</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Guliston Mebel MChJ</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>242263351</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000437095317001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №189/26 от 17.07.2026</t>
+          <t>Shartnoma №250/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1867,38 +1867,38 @@
       </c>
       <c r="C42" s="2" t="n"/>
       <c r="D42" s="2" t="n">
-        <v>6282000</v>
+        <v>2653000</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Guliston Mebel MChJ</t>
+          <t>Saodat Mehmonxona AJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>242263351</t>
+          <t>326355628</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000437095317001</t>
+          <t>20208000431759957001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №877 за поставленный товар</t>
+          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №1870 16.07.2026, QQS BILAN</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>17.07.2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1908,38 +1908,38 @@
       </c>
       <c r="C43" s="2" t="n"/>
       <c r="D43" s="2" t="n">
-        <v>4853000</v>
+        <v>8488000</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Guliston Mebel MChJ</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>242263351</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000437095317001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №139/26, QQS 12%</t>
+          <t>Shartnoma №189/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>17.07.2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1949,31 +1949,31 @@
       </c>
       <c r="C44" s="2" t="n"/>
       <c r="D44" s="2" t="n">
-        <v>789000</v>
+        <v>5574000</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Jizzax Meva-Sabzavot AJ</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>392497209</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000475480534001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №199/26 от 20.07.2026</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №877</t>
         </is>
       </c>
     </row>
@@ -1988,35 +1988,40 @@
           <t>135</t>
         </is>
       </c>
-      <c r="C45" s="2" t="n">
-        <v>10200000</v>
-      </c>
-      <c r="D45" s="2" t="n"/>
+      <c r="C45" s="2" t="n"/>
+      <c r="D45" s="2" t="n">
+        <v>4306000</v>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-7564)</t>
+          <t>Ishonch Mebel MChJ</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>16307000236105744417</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-7564 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Оплата за продукцию по договору №139/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>21.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2026,38 +2031,38 @@
       </c>
       <c r="C46" s="2" t="n"/>
       <c r="D46" s="2" t="n">
-        <v>15438000</v>
+        <v>680000</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Guliston Mebel MChJ</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>242263351</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000437095317001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №6434 ОТ 21.07.2026, В Т.Ч. НДС 12%</t>
+          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №92</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>21.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2065,40 +2070,40 @@
           <t>137</t>
         </is>
       </c>
-      <c r="C47" s="2" t="n"/>
-      <c r="D47" s="2" t="n">
-        <v>2947000</v>
-      </c>
+      <c r="C47" s="2" t="n">
+        <v>2347000</v>
+      </c>
+      <c r="D47" s="2" t="n"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Guliston Mebel MChJ</t>
+          <t>Afrosiyob Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>242263351</t>
+          <t>363004325</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000437095317001</t>
+          <t>20208000676992684001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Shartnoma №52/26 bo'yicha oldindan to'lov</t>
+          <t>Tovarlar uchun to'lov h/f №2023</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>22.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2106,40 +2111,35 @@
           <t>138</t>
         </is>
       </c>
-      <c r="C48" s="2" t="n"/>
-      <c r="D48" s="2" t="n">
-        <v>1168000</v>
-      </c>
+      <c r="C48" s="2" t="n">
+        <v>10200000</v>
+      </c>
+      <c r="D48" s="2" t="n"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Jizzax Meva-Sabzavot AJ</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>392497209</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-7564)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000475480534001</t>
+          <t>16307000236105744417</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №5876 за поставленный товар</t>
+          <t>Kredit shartnomasi L-2024-7564 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>23.07.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2149,38 +2149,38 @@
       </c>
       <c r="C49" s="2" t="n"/>
       <c r="D49" s="2" t="n">
-        <v>3761000</v>
+        <v>13700000</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Guliston Mebel MChJ</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>242263351</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000437095317001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №5868 23.07.2026, QQS bilan</t>
+          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №6434 21.07.2026, QQS BILAN</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>23.07.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2188,40 +2188,40 @@
           <t>140</t>
         </is>
       </c>
-      <c r="C50" s="2" t="n">
-        <v>1513000</v>
-      </c>
-      <c r="D50" s="2" t="n"/>
+      <c r="C50" s="2" t="n"/>
+      <c r="D50" s="2" t="n">
+        <v>2614000</v>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>НДС за июнь 2026 г.</t>
+          <t>Предоплата за товар по договору №52/26 от 21.07.2026</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2231,38 +2231,38 @@
       </c>
       <c r="C51" s="2" t="n"/>
       <c r="D51" s="2" t="n">
-        <v>1147000</v>
+        <v>620000</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Mehnat Metall MChJ</t>
+          <t>Saodat Mehmonxona AJ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>385263556</t>
+          <t>326355628</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000864317599001</t>
+          <t>20208000431759957001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2388 24.07.2026, QQS bilan</t>
+          <t>Mahsulot uchun to'lov, shartnoma №41/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2270,40 +2270,40 @@
           <t>142</t>
         </is>
       </c>
-      <c r="C52" s="2" t="n"/>
-      <c r="D52" s="2" t="n">
-        <v>14874000</v>
-      </c>
+      <c r="C52" s="2" t="n">
+        <v>6923000</v>
+      </c>
+      <c r="D52" s="2" t="n"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Mehnat Metall MChJ</t>
+          <t>Guliston Agro MChJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>385263556</t>
+          <t>219537449</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000864317599001</t>
+          <t>20208000293525169001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №8889 от 27.07.2026, в т.ч. НДС 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №45/26</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2313,38 +2313,38 @@
       </c>
       <c r="C53" s="2" t="n"/>
       <c r="D53" s="2" t="n">
-        <v>2444000</v>
+        <v>1036000</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Ishonch Meva Eksport MChJ</t>
+          <t>Denov Moy AJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>311059748</t>
+          <t>249720994</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000526392272001</t>
+          <t>20208000548053460001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №298/26, QQS 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5876</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2352,40 +2352,40 @@
           <t>144</t>
         </is>
       </c>
-      <c r="C54" s="2" t="n"/>
-      <c r="D54" s="2" t="n">
-        <v>2185000</v>
-      </c>
+      <c r="C54" s="2" t="n">
+        <v>1475000</v>
+      </c>
+      <c r="D54" s="2" t="n"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ishonch Meva Eksport MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>311059748</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000526392272001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №7962 за поставленный товар</t>
+          <t>QQS iyun 2026 uchun</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>23.07.2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="C55" s="2" t="n"/>
       <c r="D55" s="2" t="n">
-        <v>710000</v>
+        <v>3337000</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Guliston Mebel MChJ</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>242263351</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000437095317001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №189/26 от 27.07.2026</t>
+          <t>Оплата за товар по с/ф №5868 от 23.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>23.07.2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2434,40 +2434,40 @@
           <t>146</t>
         </is>
       </c>
-      <c r="C56" s="2" t="n">
-        <v>564000</v>
-      </c>
-      <c r="D56" s="2" t="n"/>
+      <c r="C56" s="2" t="n"/>
+      <c r="D56" s="2" t="n">
+        <v>1238000</v>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000239691385001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ЭЛЕКТРОЭНЕРГИЮ СОГЛАСНО СЧЕТУ</t>
+          <t>Tovar uchun to'lov, hisob-faktura №6886 23.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>23.07.2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2476,39 +2476,39 @@
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>5589000</v>
+        <v>10772000</v>
       </c>
       <c r="D57" s="2" t="n"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro MChJ</t>
+          <t>Lazzat Tekstil MChJ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>208630043</t>
+          <t>263373646</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000506769926001</t>
+          <t>20208000431006001001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №180/26 от 27.07.2026, НДС 12%</t>
+          <t>Оплата за транспортные услуги по договору №73/26</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>28.07.2026</t>
+          <t>23.07.2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2516,40 +2516,40 @@
           <t>148</t>
         </is>
       </c>
-      <c r="C58" s="2" t="n"/>
-      <c r="D58" s="2" t="n">
-        <v>6580000</v>
-      </c>
+      <c r="C58" s="2" t="n">
+        <v>11921000</v>
+      </c>
+      <c r="D58" s="2" t="n"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ishonch Meva Eksport MChJ</t>
+          <t>Afrosiyob Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>311059748</t>
+          <t>363004325</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000526392272001</t>
+          <t>20208000676992684001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №2233 за поставленный товар</t>
+          <t>Tovarlar uchun to'lov h/f №1313</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>28.07.2026</t>
+          <t>24.07.2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2559,38 +2559,38 @@
       </c>
       <c r="C59" s="2" t="n"/>
       <c r="D59" s="2" t="n">
-        <v>1775000</v>
+        <v>1018000</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Guliston Mebel MChJ</t>
+          <t>Saodat Mehmonxona AJ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>242263351</t>
+          <t>326355628</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000437095317001</t>
+          <t>20208000431759957001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №6423 за поставленный товар</t>
+          <t>Оплата за товар по счет-фактуре №2388 от 24.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>28.07.2026</t>
+          <t>24.07.2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2598,40 +2598,40 @@
           <t>150</t>
         </is>
       </c>
-      <c r="C60" s="2" t="n"/>
-      <c r="D60" s="2" t="n">
-        <v>1395000</v>
-      </c>
+      <c r="C60" s="2" t="n">
+        <v>564000</v>
+      </c>
+      <c r="D60" s="2" t="n"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Metall AJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>353860515</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000017068863001</t>
+          <t>20208000969138510001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №51/26, НДС 12%</t>
+          <t>Оплата за электроэнергию согласно счету</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>28.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2641,38 +2641,38 @@
       </c>
       <c r="C61" s="2" t="n"/>
       <c r="D61" s="2" t="n">
-        <v>1089000</v>
+        <v>2169000</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Guliston Mebel MChJ</t>
+          <t>Tong Yog'och MChJ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>242263351</t>
+          <t>205974835</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000437095317001</t>
+          <t>20208000639227281001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №6352 от 28.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за продукцию по договору №298/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>29.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2682,38 +2682,38 @@
       </c>
       <c r="C62" s="2" t="n"/>
       <c r="D62" s="2" t="n">
-        <v>11484000</v>
+        <v>1938000</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Guliston Mebel MChJ</t>
+          <t>Tong Yog'och MChJ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>242263351</t>
+          <t>205974835</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000437095317001</t>
+          <t>20208000639227281001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №100/26 от 29.07.2026</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №7962</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2723,38 +2723,38 @@
       </c>
       <c r="C63" s="2" t="n"/>
       <c r="D63" s="2" t="n">
-        <v>5015000</v>
+        <v>1575000</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Metall AJ</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>353860515</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000017068863001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №9196 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №5618</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2764,38 +2764,38 @@
       </c>
       <c r="C64" s="2" t="n"/>
       <c r="D64" s="2" t="n">
-        <v>1315000</v>
+        <v>630000</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Guliston Mebel MChJ</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>242263351</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000437095317001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №44/26 от 30.07.2026</t>
+          <t>Shartnoma №189/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>28.07.2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2805,38 +2805,38 @@
       </c>
       <c r="C65" s="2" t="n"/>
       <c r="D65" s="2" t="n">
-        <v>1190000</v>
+        <v>5838000</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ishonch Meva Eksport MChJ</t>
+          <t>Tong Yog'och MChJ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>311059748</t>
+          <t>205974835</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000526392272001</t>
+          <t>20208000639227281001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №773 за поставленный товар</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2233</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>28.07.2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2846,21 +2846,21 @@
       </c>
       <c r="C66" s="2" t="n"/>
       <c r="D66" s="2" t="n">
-        <v>736000</v>
+        <v>1019000</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Mehnat Metall MChJ</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>385263556</t>
+          <t>299374010</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000864317599001</t>
+          <t>20208000857365140001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -2870,14 +2870,14 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTN. №70/26, QQS 12%</t>
+          <t>Shartnoma №85/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>28.07.2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2885,40 +2885,40 @@
           <t>157</t>
         </is>
       </c>
-      <c r="C67" s="2" t="n">
-        <v>2505000</v>
-      </c>
-      <c r="D67" s="2" t="n"/>
+      <c r="C67" s="2" t="n"/>
+      <c r="D67" s="2" t="n">
+        <v>966000</v>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro MChJ</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>208630043</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000506769926001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №9730</t>
+          <t>Tovar uchun to'lov, hisob-faktura №6352 28.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>29.07.2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2926,35 +2926,40 @@
           <t>158</t>
         </is>
       </c>
-      <c r="C68" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D68" s="2" t="n"/>
+      <c r="C68" s="2" t="n"/>
+      <c r="D68" s="2" t="n">
+        <v>10189000</v>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Oqsaroy Bank ATB</t>
+          <t>Ishonch Mebel MChJ</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Hisob-kassa xizmati uchun haq</t>
+          <t>Shartnoma №100/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>29.07.2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2964,38 +2969,38 @@
       </c>
       <c r="C69" s="2" t="n"/>
       <c r="D69" s="2" t="n">
-        <v>14510000</v>
+        <v>924000</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Guliston Mebel MChJ</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>242263351</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000437095317001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №361 от 03.08.2026, в т.ч. НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №7978</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>29.07.2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3004,39 +3009,39 @@
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>919000</v>
+        <v>13500000</v>
       </c>
       <c r="D70" s="2" t="n"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Zarafshon Moy XK</t>
+          <t>Xiva Moy MChJ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>299258731</t>
+          <t>286051560</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000631845380001</t>
+          <t>20208000706886355001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №247/26 от 03.08.2026, НДС 12%</t>
+          <t>Tovarlar uchun to'lov h/f №1290</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>30.07.2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3046,38 +3051,38 @@
       </c>
       <c r="C71" s="2" t="n"/>
       <c r="D71" s="2" t="n">
-        <v>16915000</v>
+        <v>4449000</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Guliston Mebel MChJ</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>242263351</t>
+          <t>299374010</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000437095317001</t>
+          <t>20208000857365140001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7126</t>
+          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №9196</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>30.07.2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3085,40 +3090,40 @@
           <t>162</t>
         </is>
       </c>
-      <c r="C72" s="2" t="n">
-        <v>3671000</v>
-      </c>
-      <c r="D72" s="2" t="n"/>
+      <c r="C72" s="2" t="n"/>
+      <c r="D72" s="2" t="n">
+        <v>1167000</v>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro MChJ</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>208630043</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000506769926001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА УПАКОВОЧНЫЕ МАТЕРИАЛЫ, С/Ф №8525</t>
+          <t>Shartnoma №44/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>05.08.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3126,40 +3131,35 @@
           <t>163</t>
         </is>
       </c>
-      <c r="C73" s="2" t="n"/>
-      <c r="D73" s="2" t="n">
-        <v>4427000</v>
-      </c>
+      <c r="C73" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D73" s="2" t="n"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Guliston Mebel MChJ</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>242263351</t>
+          <t>Oqsaroy Bank ATB</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000437095317001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №76/26 от 05.08.2026</t>
+          <t>Bank xizmati uchun komissiya</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>05.08.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3167,35 +3167,40 @@
           <t>164</t>
         </is>
       </c>
-      <c r="C74" s="2" t="n">
-        <v>5081000</v>
-      </c>
-      <c r="D74" s="2" t="n"/>
+      <c r="C74" s="2" t="n"/>
+      <c r="D74" s="2" t="n">
+        <v>4820000</v>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Oqsaroy Bank ATB</t>
+          <t>Ishonch Mebel MChJ</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Перечисление заработной платы за июль 2026 г. согласно реестру №9202</t>
+          <t>Tovar uchun to'lov, hisob-faktura №7879 03.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3203,40 +3208,40 @@
           <t>165</t>
         </is>
       </c>
-      <c r="C75" s="2" t="n">
-        <v>6494000</v>
-      </c>
-      <c r="D75" s="2" t="n"/>
+      <c r="C75" s="2" t="n"/>
+      <c r="D75" s="2" t="n">
+        <v>2223000</v>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Zarafshon Moy XK</t>
+          <t>Saodat Mehmonxona AJ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>299258731</t>
+          <t>326355628</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000631845380001</t>
+          <t>20208000431759957001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №2958</t>
+          <t>Предоплата за товар по договору №152/26 от 03.08.2026</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>04.08.2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3244,40 +3249,40 @@
           <t>166</t>
         </is>
       </c>
-      <c r="C76" s="2" t="n">
-        <v>823000</v>
-      </c>
-      <c r="D76" s="2" t="n"/>
+      <c r="C76" s="2" t="n"/>
+      <c r="D76" s="2" t="n">
+        <v>5134000</v>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Chirchiq Qurilish MChJ</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>210732548</t>
+          <t>299374010</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>20208000891752591001</t>
+          <t>20208000857365140001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Ijara haqi avgust oyi uchun, shartnoma №82/23</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №7010</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>04.08.2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3285,23 +3290,23 @@
           <t>167</t>
         </is>
       </c>
-      <c r="C77" s="2" t="n">
-        <v>1615000</v>
-      </c>
-      <c r="D77" s="2" t="n"/>
+      <c r="C77" s="2" t="n"/>
+      <c r="D77" s="2" t="n">
+        <v>4029000</v>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Jizzax Savdo MChJ</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>282720080</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000165715610001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3311,14 +3316,14 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №107/26</t>
+          <t>Tovar uchun to'lov, hisob-faktura №3396 04.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>06.08.2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3326,40 +3331,40 @@
           <t>168</t>
         </is>
       </c>
-      <c r="C78" s="2" t="n">
-        <v>3428000</v>
-      </c>
-      <c r="D78" s="2" t="n"/>
+      <c r="C78" s="2" t="n"/>
+      <c r="D78" s="2" t="n">
+        <v>6386000</v>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro MChJ</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>208630043</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000506769926001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №62/26, QQS bilan</t>
+          <t>Mahsulot uchun to'lov, shartn. №175/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>11.08.2026</t>
+          <t>06.08.2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3367,40 +3372,40 @@
           <t>169</t>
         </is>
       </c>
-      <c r="C79" s="2" t="n">
-        <v>4934000</v>
-      </c>
-      <c r="D79" s="2" t="n"/>
+      <c r="C79" s="2" t="n"/>
+      <c r="D79" s="2" t="n">
+        <v>4901000</v>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro MChJ</t>
+          <t>Saodat Mehmonxona AJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>208630043</t>
+          <t>326355628</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000506769926001</t>
+          <t>20208000431759957001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №238/26</t>
+          <t>Shartnoma №145/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>14.08.2026</t>
+          <t>06.08.2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3410,38 +3415,38 @@
       </c>
       <c r="C80" s="2" t="n"/>
       <c r="D80" s="2" t="n">
-        <v>3839000</v>
+        <v>2300000</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Mehnat Metall MChJ</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>385263556</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000864317599001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №4687 за поставленный товар</t>
+          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №183/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>06.08.2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3451,38 +3456,38 @@
       </c>
       <c r="C81" s="2" t="n"/>
       <c r="D81" s="2" t="n">
-        <v>11969000</v>
+        <v>1937000</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Metall AJ</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>353860515</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000017068863001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №50/26 от 17.08.2026</t>
+          <t>Оплата за продукцию по договору №172/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>06.08.2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3490,40 +3495,40 @@
           <t>172</t>
         </is>
       </c>
-      <c r="C82" s="2" t="n"/>
-      <c r="D82" s="2" t="n">
-        <v>3919000</v>
-      </c>
+      <c r="C82" s="2" t="n">
+        <v>3930000</v>
+      </c>
+      <c r="D82" s="2" t="n"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Mehnat Metall MChJ</t>
+          <t>Afrosiyob Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>385263556</t>
+          <t>363004325</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000864317599001</t>
+          <t>20208000676992684001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №1091 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №240/26</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>06.08.2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3532,39 +3537,34 @@
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>693000</v>
+        <v>5081000</v>
       </c>
       <c r="D83" s="2" t="n"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>201122905</t>
+          <t>Oqsaroy Bank ATB</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Iyul oyi uchun ijtimoiy soliq</t>
+          <t>Перечисление заработной платы за июль 2026 г. согласно реестру №5231</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3573,39 +3573,39 @@
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>693000</v>
+        <v>823000</v>
       </c>
       <c r="D84" s="2" t="n"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Yulduz Qurilish MChJ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>273254868</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000175259122001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Налог на доходы физических лиц за июль 2026 г.</t>
+          <t>Bino ijarasi uchun to'lov avgust</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3614,39 +3614,39 @@
         </is>
       </c>
       <c r="C85" s="2" t="n">
-        <v>1235000</v>
+        <v>4937000</v>
       </c>
       <c r="D85" s="2" t="n"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Zarafshon Moy XK</t>
+          <t>Afrosiyob Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>299258731</t>
+          <t>363004325</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000631845380001</t>
+          <t>20208000676992684001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №65/26 от 17.08.2026, НДС 12%</t>
+          <t>Оплта за сырье по дог. №212/26 от 07.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3655,39 +3655,39 @@
         </is>
       </c>
       <c r="C86" s="2" t="n">
-        <v>1925000</v>
+        <v>1432000</v>
       </c>
       <c r="D86" s="2" t="n"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Zarafshon Moy XK</t>
+          <t>Xiva Moy MChJ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>299258731</t>
+          <t>286051560</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000631845380001</t>
+          <t>20208000706886355001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №112/26</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №250/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>18.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3695,40 +3695,40 @@
           <t>177</t>
         </is>
       </c>
-      <c r="C87" s="2" t="n"/>
-      <c r="D87" s="2" t="n">
-        <v>9184000</v>
-      </c>
+      <c r="C87" s="2" t="n">
+        <v>1763000</v>
+      </c>
+      <c r="D87" s="2" t="n"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Metall AJ</t>
+          <t>Xiva Moy MChJ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>353860515</t>
+          <t>286051560</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000017068863001</t>
+          <t>20208000706886355001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №4279 от 18.08.2026, в т.ч. НДС 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №220/26</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3736,40 +3736,40 @@
           <t>178</t>
         </is>
       </c>
-      <c r="C88" s="2" t="n"/>
-      <c r="D88" s="2" t="n">
-        <v>3285000</v>
-      </c>
+      <c r="C88" s="2" t="n">
+        <v>2945000</v>
+      </c>
+      <c r="D88" s="2" t="n"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Metall AJ</t>
+          <t>Shodlik Logistik MChJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>353860515</t>
+          <t>308407012</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000017068863001</t>
+          <t>20208000844690983001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Shartnoma №171/26 bo'yicha oldindan to'lov</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №138/26</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3777,40 +3777,40 @@
           <t>179</t>
         </is>
       </c>
-      <c r="C89" s="2" t="n"/>
-      <c r="D89" s="2" t="n">
-        <v>1846000</v>
-      </c>
+      <c r="C89" s="2" t="n">
+        <v>3460000</v>
+      </c>
+      <c r="D89" s="2" t="n"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Metall AJ</t>
+          <t>Xiva Moy MChJ</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>353860515</t>
+          <t>286051560</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000017068863001</t>
+          <t>20208000706886355001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО С/Ф №9435 ОТ 19.08.2026, В Т.Ч. НДС 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №7/26</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>11.08.2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3820,38 +3820,38 @@
       </c>
       <c r="C90" s="2" t="n"/>
       <c r="D90" s="2" t="n">
-        <v>3674000</v>
+        <v>920000</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Mehnat Metall MChJ</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>385263556</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000864317599001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №6361 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>Оплата за товар по счет-фактуре №7393 от 11.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>11.08.2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3860,34 +3860,39 @@
         </is>
       </c>
       <c r="C91" s="2" t="n">
-        <v>10200000</v>
+        <v>2797000</v>
       </c>
       <c r="D91" s="2" t="n"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-7564)</t>
+          <t>Durdona Meva Eksport MChJ</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>381887064</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>16307000236105744417</t>
+          <t>20208000348112932001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-7564 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Tovarlar uchun to'lov h/f №8161</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>12.08.2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3895,40 +3900,40 @@
           <t>182</t>
         </is>
       </c>
-      <c r="C92" s="2" t="n"/>
-      <c r="D92" s="2" t="n">
-        <v>3126000</v>
-      </c>
+      <c r="C92" s="2" t="n">
+        <v>6830000</v>
+      </c>
+      <c r="D92" s="2" t="n"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Ishonch Meva Eksport MChJ</t>
+          <t>Xiva Moy MChJ</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>311059748</t>
+          <t>286051560</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000526392272001</t>
+          <t>20208000706886355001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №187/26 от 21.08.2026</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №206/26</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>13.08.2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3938,21 +3943,21 @@
       </c>
       <c r="C93" s="2" t="n"/>
       <c r="D93" s="2" t="n">
-        <v>9010000</v>
+        <v>2456000</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Ishonch Meva Eksport MChJ</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>311059748</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000526392272001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -3962,14 +3967,14 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО С/Ф №510 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>Shartnoma №64/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3979,38 +3984,38 @@
       </c>
       <c r="C94" s="2" t="n"/>
       <c r="D94" s="2" t="n">
-        <v>5196000</v>
+        <v>5556000</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Mehnat Metall MChJ</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>385263556</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000864317599001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №3155 от 24.08.2026, в т.ч. НДС 12%</t>
+          <t>Shartnoma №102/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4020,38 +4025,38 @@
       </c>
       <c r="C95" s="2" t="n"/>
       <c r="D95" s="2" t="n">
-        <v>1604000</v>
+        <v>847000</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Mehnat Metall MChJ</t>
+          <t>Denov Moy AJ</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>385263556</t>
+          <t>249720994</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000864317599001</t>
+          <t>20208000548053460001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №6469 за поставленный товар</t>
+          <t>Shartnoma №39/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4059,40 +4064,40 @@
           <t>186</t>
         </is>
       </c>
-      <c r="C96" s="2" t="n">
-        <v>1229000</v>
-      </c>
-      <c r="D96" s="2" t="n"/>
+      <c r="C96" s="2" t="n"/>
+      <c r="D96" s="2" t="n">
+        <v>39960000</v>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro MChJ</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>208630043</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000506769926001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>MATERIALLAR UCHUN OLDINDAN TO'LOV, SHARTNOMA №256/26</t>
+          <t>Shartnoma №254/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4100,40 +4105,40 @@
           <t>187</t>
         </is>
       </c>
-      <c r="C97" s="2" t="n">
-        <v>1353000</v>
-      </c>
-      <c r="D97" s="2" t="n"/>
+      <c r="C97" s="2" t="n"/>
+      <c r="D97" s="2" t="n">
+        <v>1943000</v>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>НДС за июль 2026 г.</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2074</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4142,39 +4147,39 @@
         </is>
       </c>
       <c r="C98" s="2" t="n">
-        <v>1422000</v>
+        <v>693000</v>
       </c>
       <c r="D98" s="2" t="n"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>208630043</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000506769926001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №89/26</t>
+          <t>Социальный налог за июль 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4183,39 +4188,39 @@
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>1742000</v>
+        <v>693000</v>
       </c>
       <c r="D99" s="2" t="n"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>208630043</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000506769926001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №3507</t>
+          <t>JShDS iyul oyi uchun</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4223,40 +4228,40 @@
           <t>190</t>
         </is>
       </c>
-      <c r="C100" s="2" t="n"/>
-      <c r="D100" s="2" t="n">
-        <v>1728000</v>
-      </c>
+      <c r="C100" s="2" t="n">
+        <v>3330000</v>
+      </c>
+      <c r="D100" s="2" t="n"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Guliston Mebel MChJ</t>
+          <t>Afrosiyob Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>242263351</t>
+          <t>363004325</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000437095317001</t>
+          <t>20208000676992684001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №175/26 от 26.08.2026</t>
+          <t>Tovarlar uchun to'lov h/f №2058</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>18.08.2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4264,40 +4269,40 @@
           <t>191</t>
         </is>
       </c>
-      <c r="C101" s="2" t="n">
-        <v>9947000</v>
-      </c>
-      <c r="D101" s="2" t="n"/>
+      <c r="C101" s="2" t="n"/>
+      <c r="D101" s="2" t="n">
+        <v>1640000</v>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Zarafshon Moy XK</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>299258731</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000631845380001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО СЧЕТ-ФАКТУРЕ №2202</t>
+          <t>Shartnoma №211/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>18.08.2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4307,38 +4312,38 @@
       </c>
       <c r="C102" s="2" t="n"/>
       <c r="D102" s="2" t="n">
-        <v>2631000</v>
+        <v>799000</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Metall AJ</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>353860515</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000017068863001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №6328 от 27.08.2026, в т.ч. НДС 12%</t>
+          <t>SHARTNOMA №30/26 BO'YICHA OLDINDAN TO'LOV</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4348,38 +4353,38 @@
       </c>
       <c r="C103" s="2" t="n"/>
       <c r="D103" s="2" t="n">
-        <v>2366000</v>
+        <v>2365000</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Guliston Mebel MChJ</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>242263351</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000437095317001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №169/26, НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4855</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4388,22 +4393,22 @@
         </is>
       </c>
       <c r="C104" s="2" t="n">
-        <v>514000</v>
+        <v>5601000</v>
       </c>
       <c r="D104" s="2" t="n"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Xiva Moy MChJ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>286051560</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000239691385001</t>
+          <t>20208000706886355001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -4413,14 +4418,14 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ЭЛЕКТРОЭНЕРГИЮ СОГЛАСНО СЧЕТУ</t>
+          <t>Tovarlar uchun to'lov h/f №655</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4429,39 +4434,34 @@
         </is>
       </c>
       <c r="C105" s="2" t="n">
-        <v>58879000</v>
+        <v>10200000</v>
       </c>
       <c r="D105" s="2" t="n"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Ziyo Polimer XK</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>331195374</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-7564)</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000902935251001</t>
+          <t>16307000236105744417</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТРАНСПОРТНЫЕ УСЛУГИ ПО ДОГОВОРУ №104/26</t>
+          <t>Kredit shartnomasi L-2024-7564 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4471,38 +4471,38 @@
       </c>
       <c r="C106" s="2" t="n"/>
       <c r="D106" s="2" t="n">
-        <v>7567000</v>
+        <v>7815000</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Bunyodkor Qog'oz MChJ</t>
+          <t>Saodat Mehmonxona AJ</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>321993740</t>
+          <t>326355628</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000028573651001</t>
+          <t>20208000431759957001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №2614 от 31.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за продукцию по дог. №222/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4512,38 +4512,38 @@
       </c>
       <c r="C107" s="2" t="n"/>
       <c r="D107" s="2" t="n">
-        <v>2274000</v>
+        <v>3063000</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Guliston Mebel MChJ</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>242263351</t>
+          <t>299374010</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000437095317001</t>
+          <t>20208000857365140001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО С/Ф №6827 ОТ 31.08.2026, В Т.Ч. НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartn. №189/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4553,38 +4553,38 @@
       </c>
       <c r="C108" s="2" t="n"/>
       <c r="D108" s="2" t="n">
-        <v>1983000</v>
+        <v>1863000</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Metall AJ</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>353860515</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000017068863001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6249</t>
+          <t>Mahsulot uchun to'lov, shartnoma №141/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4594,38 +4594,38 @@
       </c>
       <c r="C109" s="2" t="n"/>
       <c r="D109" s="2" t="n">
-        <v>1722000</v>
+        <v>1368000</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Mehnat Metall MChJ</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>385263556</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000864317599001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №75/26, НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №6662 24.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4633,35 +4633,40 @@
           <t>200</t>
         </is>
       </c>
-      <c r="C110" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D110" s="2" t="n"/>
+      <c r="C110" s="2" t="n"/>
+      <c r="D110" s="2" t="n">
+        <v>1131000</v>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Oqsaroy Bank ATB</t>
+          <t>Ishonch Mebel MChJ</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Комиссия банка за расчетно-кассовое обслуживание за август</t>
+          <t>Mahsulot uchun to'lov, shartn. №240/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4670,39 +4675,39 @@
         </is>
       </c>
       <c r="C111" s="2" t="n">
-        <v>926000</v>
+        <v>1381000</v>
       </c>
       <c r="D111" s="2" t="n"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sharq Tikuv MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>219084070</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000228446909001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №181/26</t>
+          <t>Qo'shilgan qiymat solig'i iyul oyi</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>01.09.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4711,22 +4716,22 @@
         </is>
       </c>
       <c r="C112" s="2" t="n">
-        <v>1631000</v>
+        <v>1891000</v>
       </c>
       <c r="D112" s="2" t="n"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro MChJ</t>
+          <t>Navoiy Farm Savdo AJ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>208630043</t>
+          <t>325873186</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000506769926001</t>
+          <t>20208000184538020001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -4736,14 +4741,14 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №54/26</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №117/26</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4751,40 +4756,40 @@
           <t>203</t>
         </is>
       </c>
-      <c r="C113" s="2" t="n"/>
-      <c r="D113" s="2" t="n">
-        <v>24833000</v>
-      </c>
+      <c r="C113" s="2" t="n">
+        <v>3411000</v>
+      </c>
+      <c r="D113" s="2" t="n"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Ishonch Meva Eksport MChJ</t>
+          <t>Xiva Moy MChJ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>311059748</t>
+          <t>286051560</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000526392272001</t>
+          <t>20208000706886355001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №9578 за поставленный товар</t>
+          <t>Оплата за упаковочные материалы, с/ф №2357</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4792,40 +4797,40 @@
           <t>204</t>
         </is>
       </c>
-      <c r="C114" s="2" t="n"/>
-      <c r="D114" s="2" t="n">
-        <v>2379000</v>
-      </c>
+      <c r="C114" s="2" t="n">
+        <v>21765000</v>
+      </c>
+      <c r="D114" s="2" t="n"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Guliston Mebel MChJ</t>
+          <t>Xiva Moy MChJ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>242263351</t>
+          <t>286051560</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000437095317001</t>
+          <t>20208000706886355001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №7958 за поставленный товар</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №175/26</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4835,38 +4840,38 @@
       </c>
       <c r="C115" s="2" t="n"/>
       <c r="D115" s="2" t="n">
-        <v>4204000</v>
+        <v>1854000</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Guliston Mebel MChJ</t>
+          <t>Saodat Mehmonxona AJ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>242263351</t>
+          <t>326355628</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000437095317001</t>
+          <t>20208000431759957001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7083</t>
+          <t>Shartnoma №216/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4874,40 +4879,40 @@
           <t>206</t>
         </is>
       </c>
-      <c r="C116" s="2" t="n"/>
-      <c r="D116" s="2" t="n">
-        <v>3803000</v>
-      </c>
+      <c r="C116" s="2" t="n">
+        <v>8773000</v>
+      </c>
+      <c r="D116" s="2" t="n"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Guliston Mebel MChJ</t>
+          <t>Navoiy Farm Savdo AJ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>242263351</t>
+          <t>325873186</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000437095317001</t>
+          <t>20208000184538020001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №203/26, QQS 12%</t>
+          <t>Xom ashyo uchun to'lov, shartn. №149/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4915,40 +4920,40 @@
           <t>207</t>
         </is>
       </c>
-      <c r="C117" s="2" t="n"/>
-      <c r="D117" s="2" t="n">
-        <v>3339000</v>
-      </c>
+      <c r="C117" s="2" t="n">
+        <v>13158000</v>
+      </c>
+      <c r="D117" s="2" t="n"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Guliston Mebel MChJ</t>
+          <t>Afrosiyob Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>242263351</t>
+          <t>363004325</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000437095317001</t>
+          <t>20208000676992684001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Tovr uchun to'lov, h/f №2767 07.09.2026, QQS bilan</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №16/26</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>26.08.2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4956,40 +4961,40 @@
           <t>208</t>
         </is>
       </c>
-      <c r="C118" s="2" t="n">
-        <v>843000</v>
-      </c>
-      <c r="D118" s="2" t="n"/>
+      <c r="C118" s="2" t="n"/>
+      <c r="D118" s="2" t="n">
+        <v>7261000</v>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Chirchiq Qurilish MChJ</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>210732548</t>
+          <t>299374010</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000891752591001</t>
+          <t>20208000857365140001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Аренда помещения за сентябрь, дог. №82/23</t>
+          <t>Mahsulot uchun to'lov, shartnoma №255/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4997,40 +5002,40 @@
           <t>209</t>
         </is>
       </c>
-      <c r="C119" s="2" t="n">
-        <v>1276000</v>
-      </c>
-      <c r="D119" s="2" t="n"/>
+      <c r="C119" s="2" t="n"/>
+      <c r="D119" s="2" t="n">
+        <v>1515000</v>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Farovon Sut MChJ</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>287785562</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000674331595001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №88/26</t>
+          <t>Shartnoma №176/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5038,40 +5043,40 @@
           <t>210</t>
         </is>
       </c>
-      <c r="C120" s="2" t="n">
-        <v>2730000</v>
-      </c>
-      <c r="D120" s="2" t="n"/>
+      <c r="C120" s="2" t="n"/>
+      <c r="D120" s="2" t="n">
+        <v>1023000</v>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro MChJ</t>
+          <t>Saodat Mehmonxona AJ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>208630043</t>
+          <t>326355628</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000506769926001</t>
+          <t>20208000431759957001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №223/26</t>
+          <t>Shartnoma №1/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5080,22 +5085,22 @@
         </is>
       </c>
       <c r="C121" s="2" t="n">
-        <v>3491000</v>
+        <v>514000</v>
       </c>
       <c r="D121" s="2" t="n"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>208630043</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000506769926001</t>
+          <t>20208000969138510001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5105,14 +5110,14 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №177/26</t>
+          <t>Elektr energiyasi uchun to'lov avgust</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>28.08.2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5121,17 +5126,22 @@
         </is>
       </c>
       <c r="C122" s="2" t="n">
-        <v>5205000</v>
+        <v>2840000</v>
       </c>
       <c r="D122" s="2" t="n"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Oqsaroy Bank ATB</t>
+          <t>Shodlik Logistik MChJ</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>308407012</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000844690983001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5141,14 +5151,14 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Перечисление заработной платы за август 2026 г. согласно реестру №2692</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №251/26</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>08.09.2026</t>
+          <t>28.08.2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5156,40 +5166,40 @@
           <t>213</t>
         </is>
       </c>
-      <c r="C123" s="2" t="n"/>
-      <c r="D123" s="2" t="n">
-        <v>1081000</v>
-      </c>
+      <c r="C123" s="2" t="n">
+        <v>5388000</v>
+      </c>
+      <c r="D123" s="2" t="n"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Guliston Mebel MChJ</t>
+          <t>Afrosiyob Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>242263351</t>
+          <t>363004325</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000437095317001</t>
+          <t>20208000676992684001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №6087 от 08.09.2026, в т.ч. НДС 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №45/26</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5197,40 +5207,35 @@
           <t>214</t>
         </is>
       </c>
-      <c r="C124" s="2" t="n"/>
-      <c r="D124" s="2" t="n">
-        <v>1977000</v>
-      </c>
+      <c r="C124" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D124" s="2" t="n"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Jizzax Meva-Sabzavot AJ</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>392497209</t>
+          <t>Oqsaroy Bank ATB</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000475480534001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №209/26 от 09.09.2026</t>
+          <t>Bank xizmati uchun komissiya</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5238,40 +5243,40 @@
           <t>215</t>
         </is>
       </c>
-      <c r="C125" s="2" t="n"/>
-      <c r="D125" s="2" t="n">
-        <v>1420000</v>
-      </c>
+      <c r="C125" s="2" t="n">
+        <v>1597000</v>
+      </c>
+      <c r="D125" s="2" t="n"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Guliston Mebel MChJ</t>
+          <t>Xiva Moy MChJ</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>242263351</t>
+          <t>286051560</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000437095317001</t>
+          <t>20208000706886355001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №2423 за поставленный товар</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №22/26</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5280,39 +5285,39 @@
         </is>
       </c>
       <c r="C126" s="2" t="n">
-        <v>2928000</v>
+        <v>2125000</v>
       </c>
       <c r="D126" s="2" t="n"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Zarafshon Moy XK</t>
+          <t>Shodlik Logistik MChJ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>299258731</t>
+          <t>308407012</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000631845380001</t>
+          <t>20208000844690983001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №223/26</t>
+          <t>Tovarlar uchun to'lov h/f №7281</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>01.09.2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5320,40 +5325,40 @@
           <t>217</t>
         </is>
       </c>
-      <c r="C127" s="2" t="n">
-        <v>5552000</v>
-      </c>
-      <c r="D127" s="2" t="n"/>
+      <c r="C127" s="2" t="n"/>
+      <c r="D127" s="2" t="n">
+        <v>3222000</v>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Sharq Tikuv MChJ</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>219084070</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000228446909001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТРАНСПОРТНЫЕ УСЛУГИ ПО ДОГОВОРУ №202/26</t>
+          <t>Shartnoma №73/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>10.09.2026</t>
+          <t>01.09.2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5361,23 +5366,23 @@
           <t>218</t>
         </is>
       </c>
-      <c r="C128" s="2" t="n">
-        <v>1369000</v>
-      </c>
-      <c r="D128" s="2" t="n"/>
+      <c r="C128" s="2" t="n"/>
+      <c r="D128" s="2" t="n">
+        <v>1945000</v>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro MChJ</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>208630043</t>
+          <t>299374010</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>20208000506769926001</t>
+          <t>20208000857365140001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -5387,14 +5392,14 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №6755</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №3950</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>10.09.2026</t>
+          <t>01.09.2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5402,40 +5407,40 @@
           <t>219</t>
         </is>
       </c>
-      <c r="C129" s="2" t="n">
-        <v>3773000</v>
-      </c>
-      <c r="D129" s="2" t="n"/>
+      <c r="C129" s="2" t="n"/>
+      <c r="D129" s="2" t="n">
+        <v>1047000</v>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro MChJ</t>
+          <t>Denov Moy AJ</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>208630043</t>
+          <t>249720994</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000506769926001</t>
+          <t>20208000548053460001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №225/26</t>
+          <t>Shartnoma №120/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
+          <t>01.09.2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5444,39 +5449,39 @@
         </is>
       </c>
       <c r="C130" s="2" t="n">
-        <v>22574000</v>
+        <v>4949000</v>
       </c>
       <c r="D130" s="2" t="n"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro MChJ</t>
+          <t>Afrosiyob Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>208630043</t>
+          <t>363004325</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000506769926001</t>
+          <t>20208000676992684001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №216/26</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №251/26</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>02.09.2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5486,38 +5491,38 @@
       </c>
       <c r="C131" s="2" t="n"/>
       <c r="D131" s="2" t="n">
-        <v>7836000</v>
+        <v>1281000</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Mehnat Metall MChJ</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>385263556</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000864317599001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №80/26 от 14.09.2026</t>
+          <t>Shartnoma №124/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>02.09.2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5527,38 +5532,38 @@
       </c>
       <c r="C132" s="2" t="n"/>
       <c r="D132" s="2" t="n">
-        <v>3595000</v>
+        <v>1088000</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Guliston Mebel MChJ</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>242263351</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000437095317001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №8654 за поставленный товар</t>
+          <t>Предоплата за товар по дог. №152/26 от 02.09.2026</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>02.09.2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5566,40 +5571,40 @@
           <t>223</t>
         </is>
       </c>
-      <c r="C133" s="2" t="n"/>
-      <c r="D133" s="2" t="n">
-        <v>3591000</v>
-      </c>
+      <c r="C133" s="2" t="n">
+        <v>4239000</v>
+      </c>
+      <c r="D133" s="2" t="n"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Guliston Mebel MChJ</t>
+          <t>Xiva Moy MChJ</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>242263351</t>
+          <t>286051560</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000437095317001</t>
+          <t>20208000706886355001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №7264 за поставленный товар</t>
+          <t>Tovarlar uchun to'lov h/f №3725</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>03.09.2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5609,38 +5614,38 @@
       </c>
       <c r="C134" s="2" t="n"/>
       <c r="D134" s="2" t="n">
-        <v>2937000</v>
+        <v>2744000</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Guliston Mebel MChJ</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>242263351</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000437095317001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №151/26, НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №494303.09.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5648,40 +5653,40 @@
           <t>225</t>
         </is>
       </c>
-      <c r="C135" s="2" t="n">
-        <v>1379000</v>
-      </c>
-      <c r="D135" s="2" t="n"/>
+      <c r="C135" s="2" t="n"/>
+      <c r="D135" s="2" t="n">
+        <v>862000</v>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Sharq Tikuv MChJ</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>219084070</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20208000228446909001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №5629</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №243/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5689,40 +5694,40 @@
           <t>226</t>
         </is>
       </c>
-      <c r="C136" s="2" t="n">
-        <v>6672000</v>
-      </c>
-      <c r="D136" s="2" t="n"/>
+      <c r="C136" s="2" t="n"/>
+      <c r="D136" s="2" t="n">
+        <v>565000</v>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro MChJ</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>208630043</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20208000506769926001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №719</t>
+          <t>Оплата по счет-фактуре №7102 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5731,39 +5736,34 @@
         </is>
       </c>
       <c r="C137" s="2" t="n">
-        <v>710000</v>
+        <v>5205000</v>
       </c>
       <c r="D137" s="2" t="n"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>201122905</t>
+          <t>Oqsaroy Bank ATB</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>УПЛАТА СОЦИАЛЬНОГО НАЛОГА ЗА АВГУСТ</t>
+          <t>Avgust oyi uchun ish haqi, reestr №214</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5771,40 +5771,40 @@
           <t>228</t>
         </is>
       </c>
-      <c r="C138" s="2" t="n">
-        <v>710000</v>
-      </c>
-      <c r="D138" s="2" t="n"/>
+      <c r="C138" s="2" t="n"/>
+      <c r="D138" s="2" t="n">
+        <v>3287000</v>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Denov Moy AJ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>249720994</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000548053460001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Jismoniy shaxslar daromad solig'i avgust 2026</t>
+          <t>Mahsulot uchun to'lov, shartnoma №183/26, QS 12%</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5812,40 +5812,40 @@
           <t>229</t>
         </is>
       </c>
-      <c r="C139" s="2" t="n">
-        <v>7499000</v>
-      </c>
-      <c r="D139" s="2" t="n"/>
+      <c r="C139" s="2" t="n"/>
+      <c r="D139" s="2" t="n">
+        <v>3061000</v>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Kamalak Un Mahsulotlari XK</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>328064160</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000364512854001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №222/26</t>
+          <t>Оплата по счет-фактуре №5028 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>17.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5853,23 +5853,23 @@
           <t>230</t>
         </is>
       </c>
-      <c r="C140" s="2" t="n">
-        <v>7267000</v>
-      </c>
-      <c r="D140" s="2" t="n"/>
+      <c r="C140" s="2" t="n"/>
+      <c r="D140" s="2" t="n">
+        <v>990000</v>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro MChJ</t>
+          <t>Namangan Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>208630043</t>
+          <t>299374010</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20208000506769926001</t>
+          <t>20208000857365140001</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -5879,14 +5879,14 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №157/26</t>
+          <t>Shartnoma №136/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>20.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5894,35 +5894,40 @@
           <t>231</t>
         </is>
       </c>
-      <c r="C141" s="2" t="n">
-        <v>10200000</v>
-      </c>
-      <c r="D141" s="2" t="n"/>
+      <c r="C141" s="2" t="n"/>
+      <c r="D141" s="2" t="n">
+        <v>682000</v>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-7564)</t>
+          <t>Saodat Mehmonxona AJ</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>326355628</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>16307000236105744417</t>
+          <t>20208000431759957001</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-7564 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Mahsulot uchun to'lov, shartnoma №22/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5930,23 +5935,23 @@
           <t>232</t>
         </is>
       </c>
-      <c r="C142" s="2" t="n"/>
-      <c r="D142" s="2" t="n">
-        <v>3652000</v>
-      </c>
+      <c r="C142" s="2" t="n">
+        <v>843000</v>
+      </c>
+      <c r="D142" s="2" t="n"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Guliston Mebel MChJ</t>
+          <t>Yulduz Qurilish MChJ</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>242263351</t>
+          <t>273254868</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>20208000437095317001</t>
+          <t>20208000175259122001</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -5956,14 +5961,14 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №28/26, НДС 12%</t>
+          <t>АРЕНДА ПОМЕЩЕНИЯ ЗА СЕНТЯБРЬ, ДОГ. №96/21</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5971,40 +5976,40 @@
           <t>233</t>
         </is>
       </c>
-      <c r="C143" s="2" t="n"/>
-      <c r="D143" s="2" t="n">
-        <v>2587000</v>
-      </c>
+      <c r="C143" s="2" t="n">
+        <v>7299000</v>
+      </c>
+      <c r="D143" s="2" t="n"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Guliston Mebel MChJ</t>
+          <t>Shodlik Logistik MChJ</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>242263351</t>
+          <t>308407012</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>20208000437095317001</t>
+          <t>20208000844690983001</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №20/26, НДС 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №94/26</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>08.09.2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6012,40 +6017,40 @@
           <t>234</t>
         </is>
       </c>
-      <c r="C144" s="2" t="n">
-        <v>1431000</v>
-      </c>
-      <c r="D144" s="2" t="n"/>
+      <c r="C144" s="2" t="n"/>
+      <c r="D144" s="2" t="n">
+        <v>2097000</v>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>НДС за август 2026 г.</t>
+          <t>Shartnoma №4/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>08.09.2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6053,40 +6058,40 @@
           <t>235</t>
         </is>
       </c>
-      <c r="C145" s="2" t="n">
-        <v>1759000</v>
-      </c>
-      <c r="D145" s="2" t="n"/>
+      <c r="C145" s="2" t="n"/>
+      <c r="D145" s="2" t="n">
+        <v>2001000</v>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro MChJ</t>
+          <t>Denov Moy AJ</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>208630043</t>
+          <t>249720994</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>20208000506769926001</t>
+          <t>20208000548053460001</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №7786</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №8337</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6094,40 +6099,40 @@
           <t>236</t>
         </is>
       </c>
-      <c r="C146" s="2" t="n">
-        <v>1817000</v>
-      </c>
-      <c r="D146" s="2" t="n"/>
+      <c r="C146" s="2" t="n"/>
+      <c r="D146" s="2" t="n">
+        <v>5412000</v>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro MChJ</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>208630043</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>20208000506769926001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №162/26</t>
+          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №7240 09.09.2026, QQS BILAN</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6135,40 +6140,40 @@
           <t>237</t>
         </is>
       </c>
-      <c r="C147" s="2" t="n">
-        <v>3405000</v>
-      </c>
-      <c r="D147" s="2" t="n"/>
+      <c r="C147" s="2" t="n"/>
+      <c r="D147" s="2" t="n">
+        <v>4835000</v>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Farovon Sut MChJ</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>287785562</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>20208000674331595001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №155/26</t>
+          <t>Mahsulot uchun to'lov, shartn. №150/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6176,40 +6181,40 @@
           <t>238</t>
         </is>
       </c>
-      <c r="C148" s="2" t="n">
-        <v>3689000</v>
-      </c>
-      <c r="D148" s="2" t="n"/>
+      <c r="C148" s="2" t="n"/>
+      <c r="D148" s="2" t="n">
+        <v>4491000</v>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro MChJ</t>
+          <t>Saodat Mehmonxona AJ</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>208630043</t>
+          <t>326355628</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>20208000506769926001</t>
+          <t>20208000431759957001</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА МАТЕРИАЛЫ ПО ДОГОВОРУ №25/26</t>
+          <t>Yetkazilgan tovar ucun to'lov h/f №1440</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6217,40 +6222,40 @@
           <t>239</t>
         </is>
       </c>
-      <c r="C149" s="2" t="n">
-        <v>9257000</v>
-      </c>
-      <c r="D149" s="2" t="n"/>
+      <c r="C149" s="2" t="n"/>
+      <c r="D149" s="2" t="n">
+        <v>1548000</v>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro MChJ</t>
+          <t>Saodat Mehmonxona AJ</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>208630043</t>
+          <t>326355628</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>20208000506769926001</t>
+          <t>20208000431759957001</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТРАНСПОРТНЫЕ УСЛУГИ ПО ДОГОВОРУ №73/26</t>
+          <t>Mahsulot uchun to'lov, shartn. №89/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>22.09.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6260,38 +6265,38 @@
       </c>
       <c r="C150" s="2" t="n"/>
       <c r="D150" s="2" t="n">
-        <v>1725000</v>
+        <v>1043000</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Guliston Mebel MChJ</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>242263351</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>20208000437095317001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №204/26 от 22.09.2026</t>
+          <t>Mahsulot uchun to'lov, shartnoma №248/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>23.09.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6301,38 +6306,38 @@
       </c>
       <c r="C151" s="2" t="n"/>
       <c r="D151" s="2" t="n">
-        <v>2045000</v>
+        <v>982000</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Guliston Mebel MChJ</t>
+          <t>Saodat Mehmonxona AJ</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>242263351</t>
+          <t>326355628</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>20208000437095317001</t>
+          <t>20208000431759957001</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Shartnoma №270/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товар по с/ф №4006 от 09.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>23.09.2026</t>
+          <t>10.09.2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6340,40 +6345,40 @@
           <t>242</t>
         </is>
       </c>
-      <c r="C152" s="2" t="n">
-        <v>527000</v>
-      </c>
-      <c r="D152" s="2" t="n"/>
+      <c r="C152" s="2" t="n"/>
+      <c r="D152" s="2" t="n">
+        <v>839000</v>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>20208000239691385001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию за сентябрь 2026 г.</t>
+          <t>Shartnoma №268/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>24.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -6383,38 +6388,38 @@
       </c>
       <c r="C153" s="2" t="n"/>
       <c r="D153" s="2" t="n">
-        <v>1410000</v>
+        <v>7249000</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Guliston Mebel MChJ</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>242263351</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>20208000437095317001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Shartnoma №184/26 bo'yicha oldindan to'lov</t>
+          <t>Shartnoma №7/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>24.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -6422,40 +6427,40 @@
           <t>244</t>
         </is>
       </c>
-      <c r="C154" s="2" t="n">
-        <v>10104000</v>
-      </c>
-      <c r="D154" s="2" t="n"/>
+      <c r="C154" s="2" t="n"/>
+      <c r="D154" s="2" t="n">
+        <v>5085000</v>
+      </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Farovon Sut MChJ</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>287785562</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>20208000674331595001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №176/26 от 24.09.2026, НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №1634</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -6465,38 +6470,38 @@
       </c>
       <c r="C155" s="2" t="n"/>
       <c r="D155" s="2" t="n">
-        <v>16269000</v>
+        <v>2580000</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Guliston Mebel MChJ</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>242263351</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>20208000437095317001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №270/26, НДС 12%</t>
+          <t>Предоплата за товар по дог. №79/26 от 14.09.2026</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -6506,38 +6511,38 @@
       </c>
       <c r="C156" s="2" t="n"/>
       <c r="D156" s="2" t="n">
-        <v>7998000</v>
+        <v>1364000</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Mehnat Metall MChJ</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>385263556</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>20208000864317599001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №85/26, НДС 12%</t>
+          <t>Предоплата за товар по договору №57/26 от 14.09.2026</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -6545,40 +6550,40 @@
           <t>247</t>
         </is>
       </c>
-      <c r="C157" s="2" t="n"/>
-      <c r="D157" s="2" t="n">
-        <v>7917000</v>
-      </c>
+      <c r="C157" s="2" t="n">
+        <v>4566000</v>
+      </c>
+      <c r="D157" s="2" t="n"/>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Guliston Mebel MChJ</t>
+          <t>Afrosiyob Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>242263351</t>
+          <t>363004325</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>20208000437095317001</t>
+          <t>20208000676992684001</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №55/26 от 28.09.2026</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №7/26</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -6587,39 +6592,39 @@
         </is>
       </c>
       <c r="C158" s="2" t="n">
-        <v>1498000</v>
+        <v>28839000</v>
       </c>
       <c r="D158" s="2" t="n"/>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro MChJ</t>
+          <t>Afrosiyob Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>208630043</t>
+          <t>363004325</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>20208000506769926001</t>
+          <t>20208000676992684001</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №80/26, QQS bilan</t>
+          <t>Предоплата за материалы по договору №296/26</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -6627,40 +6632,40 @@
           <t>249</t>
         </is>
       </c>
-      <c r="C159" s="2" t="n">
-        <v>1889000</v>
-      </c>
-      <c r="D159" s="2" t="n"/>
+      <c r="C159" s="2" t="n"/>
+      <c r="D159" s="2" t="n">
+        <v>1267000</v>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro MChJ</t>
+          <t>Saodat Mehmonxona AJ</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>208630043</t>
+          <t>326355628</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>20208000506769926001</t>
+          <t>20208000431759957001</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №26/26</t>
+          <t>Tovar uchun to'lov, hisob-faktura №4509 15.09.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>29.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -6668,40 +6673,40 @@
           <t>250</t>
         </is>
       </c>
-      <c r="C160" s="2" t="n"/>
-      <c r="D160" s="2" t="n">
-        <v>5964000</v>
-      </c>
+      <c r="C160" s="2" t="n">
+        <v>11317000</v>
+      </c>
+      <c r="D160" s="2" t="n"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Guliston Mebel MChJ</t>
+          <t>Navoiy Farm Savdo AJ</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>242263351</t>
+          <t>325873186</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>20208000437095317001</t>
+          <t>20208000184538020001</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №1742 за поставленный товар</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №201/26</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>29.09.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -6711,38 +6716,38 @@
       </c>
       <c r="C161" s="2" t="n"/>
       <c r="D161" s="2" t="n">
-        <v>4197000</v>
+        <v>1738000</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Guliston Mebel MChJ</t>
+          <t>Saodat Mehmonxona AJ</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>242263351</t>
+          <t>326355628</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>20208000437095317001</t>
+          <t>20208000431759957001</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №9558 ОТ 29.09.2026, В Т.Ч. НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №7456</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>30.09.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -6752,38 +6757,38 @@
       </c>
       <c r="C162" s="2" t="n"/>
       <c r="D162" s="2" t="n">
-        <v>4526000</v>
+        <v>1665000</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Guliston Mebel MChJ</t>
+          <t>Ishonch Mebel MChJ</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>242263351</t>
+          <t>226335184</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>20208000437095317001</t>
+          <t>20208000709531741001</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №15/26 от 30.09.2026</t>
+          <t>Mahsulot uchun to'lov, shartnoma №69/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>30.09.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -6792,53 +6797,1155 @@
         </is>
       </c>
       <c r="C163" s="2" t="n">
-        <v>300000</v>
+        <v>710000</v>
       </c>
       <c r="D163" s="2" t="n"/>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Oqsaroy Bank ATB</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Комиссия за перевод</t>
+          <t>Ijtimoiy soliq avgust 2026</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Jami aylanma:</t>
-        </is>
-      </c>
-      <c r="C164" s="4" t="n">
-        <v>365508000</v>
-      </c>
-      <c r="D164" s="4" t="n">
-        <v>358108000</v>
+          <t>16.09.2026</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="n">
+        <v>710000</v>
+      </c>
+      <c r="D164" s="2" t="n"/>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>201122905</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>23402000300100001010</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>00014</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Налог на доходы физических лиц за август 2026 г.</t>
+        </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
+          <t>16.09.2026</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="n">
+        <v>3208000</v>
+      </c>
+      <c r="D165" s="2" t="n"/>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Afrosiyob Tur Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>363004325</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>20208000676992684001</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №243/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>16.09.2026</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="n">
+        <v>4857000</v>
+      </c>
+      <c r="D166" s="2" t="n"/>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Shodlik Logistik MChJ</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>308407012</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>20208000844690983001</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №141/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>16.09.2026</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="n">
+        <v>6853000</v>
+      </c>
+      <c r="D167" s="2" t="n"/>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Xiva Moy MChJ</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>286051560</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>20208000706886355001</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Transport xizmatlari ucun to'lov, shartnoma №27/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>17.09.2026</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="n"/>
+      <c r="D168" s="2" t="n">
+        <v>1111000</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Namangan Qog'oz MChJ</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>299374010</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>20208000857365140001</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Shartnoma №130/26 bo'yicha oldindan to'lov</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>18.09.2026</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="n"/>
+      <c r="D169" s="2" t="n">
+        <v>746000</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Saodat Mehmonxona AJ</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>326355628</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>20208000431759957001</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Mahsulot uchun to'lov, shartn. №173/26, QQS 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>20.09.2026</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="n">
+        <v>10200000</v>
+      </c>
+      <c r="D170" s="2" t="n"/>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-7564)</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>16307000236105744417</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Kredit shartnomasi L-2024-7564 bo'yicha navbatdagi to'lov (09.2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>21.09.2026</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="n"/>
+      <c r="D171" s="2" t="n">
+        <v>3581000</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Ishonch Mebel MChJ</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>226335184</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>20208000709531741001</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Yetkazilgan tovar uchun to'lov h/f №8695</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>21.09.2026</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="n"/>
+      <c r="D172" s="2" t="n">
+        <v>2623000</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Ishonch Mebel MChJ</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>226335184</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>20208000709531741001</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Shartnoma №287/26 bo'yicha oldindan to'lov</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>21.09.2026</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="n"/>
+      <c r="D173" s="2" t="n">
+        <v>2342000</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Ishonch Mebel MChJ</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>226335184</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>20208000709531741001</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Yetkzilgan tovar uchun to'lov h/f №7311</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>21.09.2026</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="n"/>
+      <c r="D174" s="2" t="n">
+        <v>1885000</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Saodat Mehmonxona AJ</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>326355628</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>20208000431759957001</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Оплата за продукцию по договору №153/26, НДС 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>21.09.2026</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="n"/>
+      <c r="D175" s="2" t="n">
+        <v>586000</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Ishonch Mebel MChJ</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>226335184</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>20208000709531741001</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Shartnoma №178/26 bo'yicha oldindan to'lov</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>21.09.2026</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="n"/>
+      <c r="D176" s="2" t="n">
+        <v>557000</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Saodat Mehmonxona AJ</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>326355628</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>20208000431759957001</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Оплата за товар по счет-фактуре №6650 от 21.09.2026, в т.ч. НДС 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>21.09.2026</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="n">
+        <v>3207000</v>
+      </c>
+      <c r="D177" s="2" t="n"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Xiva Moy MChJ</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>286051560</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>20208000706886355001</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>TOVARLAR UCHUN TO'LOV H/F №6021</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>21.09.2026</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="n">
+        <v>6297000</v>
+      </c>
+      <c r="D178" s="2" t="n"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Zafar Qurilish AJ</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>272008031</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>20208000571561011001</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Xom ashyo uchun to'lov, shartn. №228/26, QQS bilan</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>23.09.2026</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="n">
+        <v>1427000</v>
+      </c>
+      <c r="D179" s="2" t="n"/>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>201122905</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>23402000300100001010</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>00014</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Qo'shilgan qiymat solig'i avgust oyi</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>24.09.2026</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="n"/>
+      <c r="D180" s="2" t="n">
+        <v>6122000</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Ishonch Mebel MChJ</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>226335184</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>20208000709531741001</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Tovar uchun to'lov, h/f №2919 24.09.2026, QQS bilan</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>24.09.2026</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="n"/>
+      <c r="D181" s="2" t="n">
+        <v>762000</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Ishonch Mebel MChJ</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>226335184</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>20208000709531741001</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Shartnoma №240/26 bo'yicha oldindan to'lov</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>24.09.2026</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="n"/>
+      <c r="D182" s="2" t="n">
+        <v>670000</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Ishonch Mebel MChJ</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>226335184</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>20208000709531741001</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Yetkazilgan tova uchun to'lov h/f №8939</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>24.09.2026</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="n">
+        <v>6400000</v>
+      </c>
+      <c r="D183" s="2" t="n"/>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Afrosiyob Tur Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>363004325</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>20208000676992684001</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Tovarlar uchun to'lov h/f №4911</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>25.09.2026</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="n"/>
+      <c r="D184" s="2" t="n">
+        <v>18414000</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Tong Yog'och MChJ</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>205974835</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>20208000639227281001</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Mahsulot uchun to'lov, shartnoma №145/26, QQS 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>25.09.2026</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="n">
+        <v>527000</v>
+      </c>
+      <c r="D185" s="2" t="n"/>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Hududiy elektr tarmoqlari AJ</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>200933985</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>20208000969138510001</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Elektr energiyasi uchun to'lov sentyabr</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="n"/>
+      <c r="D186" s="2" t="n">
+        <v>8573000</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Ishonch Mebel MChJ</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>226335184</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>20208000709531741001</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Shartnoma №134/26 bo'yicha oldindan to'lov</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="n"/>
+      <c r="D187" s="2" t="n">
+        <v>1463000</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Ishonch Mebel MChJ</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>226335184</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>20208000709531741001</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Tovar uchun to'lov, hisob-faktura №1544 28.09.2026, QQS bilan</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="n">
+        <v>9123000</v>
+      </c>
+      <c r="D188" s="2" t="n"/>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Shodlik Logistik MChJ</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>308407012</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>20208000844690983001</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Оплата за сырье по договору №37/26 от 28.09.2026, НДС 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="n"/>
+      <c r="D189" s="2" t="n">
+        <v>4475000</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Ishonch Mebel MChJ</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>226335184</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>20208000709531741001</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Yetkazilgan tovar uchun to'lov h/f №1657</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D190" s="2" t="n"/>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Oqsaroy Bank ATB</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>45994000900000001001</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Bank xizmati uchun komissiya</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Jami aylanma:</t>
+        </is>
+      </c>
+      <c r="C191" s="4" t="n">
+        <v>364277000</v>
+      </c>
+      <c r="D191" s="4" t="n">
+        <v>356877000</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
           <t>Davr oxiridagi qoldiq:</t>
         </is>
       </c>
-      <c r="C165" s="4" t="n">
+      <c r="C192" s="4" t="n">
         <v>59800000</v>
       </c>
-      <c r="D165" s="4" t="n"/>
+      <c r="D192" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
